--- a/app/src/main/assets/report_template.xlsx
+++ b/app/src/main/assets/report_template.xlsx
@@ -2881,7 +2881,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AV89"/>
+  <dimension ref="A1:AU89"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9" zeroHeight="1"/>
   <cols>
     <col min="1" max="3" customWidth="1" width="4.4179688" style="1"/>
@@ -3681,7 +3681,9 @@
       <c r="R20" s="33">
         <v>1.0</v>
       </c>
-      <c r="S20" s="65"/>
+      <c r="S20" s="65" t="s">
+        <v>445</v>
+      </c>
       <c r="T20" s="65"/>
       <c r="U20" s="10"/>
       <c r="V20" s="66"/>
@@ -3721,11 +3723,11 @@
       <c r="Z21" s="67"/>
       <c r="AB21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>0.8525077071648484</v>
+        <v>1.8689702766724814</v>
       </c>
       <c r="AC21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>1.6647372312956183</v>
+        <v>0.5379647872883688</v>
       </c>
       <c r="AD21" s="69" t="e">
         <f ca="1">#REF!</f>
@@ -3733,19 +3735,19 @@
       </c>
       <c r="AE21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>5.49717351781449</v>
+        <v>1.684582443118473</v>
       </c>
       <c r="AF21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>2.085021734788358</v>
+        <v>2.761086214711575</v>
       </c>
       <c r="AG21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>5.548490553290781</v>
+        <v>1.7427218452137272</v>
       </c>
       <c r="AH21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>2.717756598106158</v>
+        <v>1.0583092932531863</v>
       </c>
       <c r="AM21" s="70"/>
       <c r="AN21" s="70">
@@ -5714,391 +5716,391 @@
     <row r="89" spans="8:8" ht="15.0" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="386">
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:A19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D36:D43"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="R55:R56"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="AF27:AF28"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="AB21:AB22"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="AE21:AE22"/>
     <mergeCell ref="AF21:AF22"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="AD21:AD22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="Q21:Q22"/>
     <mergeCell ref="AG21:AG22"/>
     <mergeCell ref="AH21:AH22"/>
-    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="D28:D35"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="J28:J43"/>
+    <mergeCell ref="P42:P43"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="J44:J59"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="Q34:Q35"/>
     <mergeCell ref="B36:B51"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="J28:J43"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="B52:B67"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="C44:C59"/>
+    <mergeCell ref="A52:A67"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="R34:R35"/>
+    <mergeCell ref="D36:D43"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="O42:O43"/>
+    <mergeCell ref="N42:N43"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="Q42:Q43"/>
+    <mergeCell ref="R42:R43"/>
+    <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="N15:N16"/>
-    <mergeCell ref="R34:R35"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="O42:O43"/>
-    <mergeCell ref="N42:N43"/>
-    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="AB21:AB22"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="AB27:AB28"/>
-    <mergeCell ref="C28:C43"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="A36:A51"/>
-    <mergeCell ref="M55:M56"/>
-    <mergeCell ref="D60:D67"/>
-    <mergeCell ref="A77:T77"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="S28:T35"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="AC21:AC22"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M42:M43"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="C44:C59"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="F1:O2"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="B20:B35"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="S36:T43"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="AG27:AG28"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="AC27:AC28"/>
-    <mergeCell ref="AD27:AD28"/>
-    <mergeCell ref="AH27:AH28"/>
-    <mergeCell ref="P34:P35"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="J12:J27"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="K3:R3"/>
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="S4:T11"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="E12:E14"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="M13:M14"/>
-    <mergeCell ref="D4:D11"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="AE27:AE28"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="S20:T27"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="N37:N38"/>
     <mergeCell ref="M37:M38"/>
     <mergeCell ref="L37:L38"/>
     <mergeCell ref="K37:K38"/>
-    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="D4:D11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J12:J27"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="S20:T27"/>
+    <mergeCell ref="Z20:Z21"/>
     <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="AE27:AE28"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="AF27:AF28"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="AB27:AB28"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="AG27:AG28"/>
+    <mergeCell ref="AH27:AH28"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="R55:R56"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="C28:C43"/>
+    <mergeCell ref="A36:A51"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="F1:O2"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="S36:T43"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="D12:D19"/>
+    <mergeCell ref="S12:T19"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="S28:T35"/>
+    <mergeCell ref="B20:B35"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="D60:D67"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="A77:T77"/>
+    <mergeCell ref="N55:N56"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="R63:R64"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="Q66:Q67"/>
+    <mergeCell ref="P66:P67"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="N66:N67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="O61:O62"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="O63:O64"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="A72:E76"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="N61:N62"/>
+    <mergeCell ref="O66:O67"/>
+    <mergeCell ref="P61:P62"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="R61:R62"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="Q63:Q64"/>
+    <mergeCell ref="P63:P64"/>
+    <mergeCell ref="M63:M64"/>
+    <mergeCell ref="N63:N64"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="S44:T51"/>
+    <mergeCell ref="C12:C27"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="D44:D51"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="J4:J11"/>
+    <mergeCell ref="D20:D27"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="C60:C67"/>
     <mergeCell ref="B68:D69"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="T60:T67"/>
+    <mergeCell ref="L55:L56"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="I47:I49"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="J60:J67"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="K61:K62"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="R66:R67"/>
+    <mergeCell ref="L63:L64"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="J68:T76"/>
+    <mergeCell ref="F72:I76"/>
+    <mergeCell ref="E79:P80"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="R53:R54"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="Q53:Q54"/>
     <mergeCell ref="P53:P54"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="E52:E54"/>
     <mergeCell ref="F52:F54"/>
-    <mergeCell ref="P61:P62"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="D20:D27"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="P66:P67"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="R61:R62"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="K42:K43"/>
-    <mergeCell ref="N34:N35"/>
-    <mergeCell ref="R42:R43"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="K3:R3"/>
-    <mergeCell ref="S4:T11"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="N55:N56"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="Q66:Q67"/>
-    <mergeCell ref="A20:A35"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="M63:M64"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="P63:P64"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="N63:N64"/>
-    <mergeCell ref="O66:O67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="D44:D51"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="R53:R54"/>
-    <mergeCell ref="C60:C67"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="N61:N62"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="T52:T59"/>
-    <mergeCell ref="D52:D59"/>
-    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="H52:H54"/>
     <mergeCell ref="G44:G46"/>
-    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="N47:N48"/>
     <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="Q63:Q64"/>
-    <mergeCell ref="E52:E54"/>
     <mergeCell ref="Q61:Q62"/>
     <mergeCell ref="F70:G70"/>
     <mergeCell ref="E69:F69"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="N50:N51"/>
+    <mergeCell ref="O50:O51"/>
+    <mergeCell ref="D52:D59"/>
+    <mergeCell ref="T52:T59"/>
+    <mergeCell ref="F71:G71"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="H70:I70"/>
     <mergeCell ref="E63:E65"/>
     <mergeCell ref="F60:F62"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="M50:M51"/>
-    <mergeCell ref="N50:N51"/>
-    <mergeCell ref="K53:K54"/>
     <mergeCell ref="G69:I69"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="O50:O51"/>
-    <mergeCell ref="Q53:Q54"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="O61:O62"/>
-    <mergeCell ref="C12:C27"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="L55:L56"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="F72:I76"/>
-    <mergeCell ref="E79:P80"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="J60:J67"/>
-    <mergeCell ref="K66:K67"/>
-    <mergeCell ref="R66:R67"/>
-    <mergeCell ref="N66:N67"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="P42:P43"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="J44:J59"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="AE21:AE22"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="B52:B67"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="A52:A67"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="D28:D35"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="O63:O64"/>
-    <mergeCell ref="M66:M67"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="S12:T19"/>
-    <mergeCell ref="D12:D19"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:E76"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="O10:O11"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="H47:H49"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="T60:T67"/>
-    <mergeCell ref="J68:T76"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="S44:T51"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="K61:K62"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="R63:R64"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="J4:J11"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="I47:I49"/>
-    <mergeCell ref="G68:I68"/>
     <mergeCell ref="H71:I71"/>
   </mergeCells>
   <pageMargins left="0.118055555555556" right="0.275694444444444" top="0.157638888888889" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6108,7 +6110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BB103"/>
+  <dimension ref="A1:BA103"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="0.56640625" style="102"/>
@@ -13193,30 +13195,31 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="AK17:AK18"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AK11:AK12"/>
-    <mergeCell ref="AK20:AK21"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="M17:M18"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="AK8:AK9"/>
     <mergeCell ref="M5:M6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="AK14:AK15"/>
     <mergeCell ref="M8:M9"/>
+    <mergeCell ref="AK11:AK12"/>
     <mergeCell ref="M20:M21"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AK14:AK15"/>
-    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AK20:AK21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
@@ -13225,7 +13228,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X1253"/>
+  <dimension ref="A1:W1253"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="4.4179688" style="1"/>
@@ -23888,77 +23891,77 @@
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="E10:E12"/>
     <mergeCell ref="I10:I12"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="J10:J12"/>
     <mergeCell ref="A16:A21"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C4:C6"/>
     <mergeCell ref="F13:F15"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="B19:B21"/>
     <mergeCell ref="I25:I27"/>
     <mergeCell ref="G25:G27"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="C19:C21"/>
     <mergeCell ref="B16:B18"/>
+    <mergeCell ref="E13:E15"/>
     <mergeCell ref="G19:G21"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="I19:I21"/>
     <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="E19:E21"/>
   </mergeCells>
   <pageMargins left="0.118055555555556" right="0.275694444444444" top="0.157638888888889" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9"/>
@@ -23967,7 +23970,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="2" max="2" customWidth="0" width="10.0" style="1"/>
@@ -24455,12 +24458,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" customWidth="1" width="9.136719" style="102"/>
@@ -24730,5 +24734,6 @@
     <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
--- a/app/src/main/assets/report_template.xlsx
+++ b/app/src/main/assets/report_template.xlsx
@@ -2881,7 +2881,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU89"/>
+  <dimension ref="A1:AV89"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9" zeroHeight="1"/>
   <cols>
     <col min="1" max="3" customWidth="1" width="4.4179688" style="1"/>
@@ -3681,9 +3681,7 @@
       <c r="R20" s="33">
         <v>1.0</v>
       </c>
-      <c r="S20" s="65" t="s">
-        <v>445</v>
-      </c>
+      <c r="S20" s="65"/>
       <c r="T20" s="65"/>
       <c r="U20" s="10"/>
       <c r="V20" s="66"/>
@@ -3723,11 +3721,11 @@
       <c r="Z21" s="67"/>
       <c r="AB21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>1.8689702766724814</v>
+        <v>1.3554261094067306</v>
       </c>
       <c r="AC21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>0.5379647872883688</v>
+        <v>4.681319513495437</v>
       </c>
       <c r="AD21" s="69" t="e">
         <f ca="1">#REF!</f>
@@ -3735,19 +3733,19 @@
       </c>
       <c r="AE21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>1.684582443118473</v>
+        <v>5.806137966618905</v>
       </c>
       <c r="AF21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>2.761086214711575</v>
+        <v>0.5321040204887733</v>
       </c>
       <c r="AG21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>1.7427218452137272</v>
+        <v>3.0824391847273906</v>
       </c>
       <c r="AH21" s="69">
         <f>RAND()*(9-3)</f>
-        <v>1.0583092932531863</v>
+        <v>0.22327309887403324</v>
       </c>
       <c r="AM21" s="70"/>
       <c r="AN21" s="70">
@@ -5716,391 +5714,391 @@
     <row r="89" spans="8:8" ht="15.0" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="386">
-    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:A19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D36:D43"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="R55:R56"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="AF27:AF28"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="AF21:AF22"/>
+    <mergeCell ref="K7:K8"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="AC21:AC22"/>
-    <mergeCell ref="AB21:AB22"/>
-    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="M21:M22"/>
     <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="AD21:AD22"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="AE21:AE22"/>
-    <mergeCell ref="AF21:AF22"/>
     <mergeCell ref="AG21:AG22"/>
     <mergeCell ref="AH21:AH22"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="D28:D35"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="B36:B51"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K34:K35"/>
     <mergeCell ref="J28:J43"/>
-    <mergeCell ref="P42:P43"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="J44:J59"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="B36:B51"/>
-    <mergeCell ref="B52:B67"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="C44:C59"/>
-    <mergeCell ref="A52:A67"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="R34:R35"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="Q42:Q43"/>
     <mergeCell ref="M34:M35"/>
-    <mergeCell ref="P34:P35"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N34:N35"/>
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="R34:R35"/>
-    <mergeCell ref="D36:D43"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="K42:K43"/>
     <mergeCell ref="O42:O43"/>
     <mergeCell ref="N42:N43"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="AB21:AB22"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="AB27:AB28"/>
+    <mergeCell ref="C28:C43"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="A36:A51"/>
+    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="D60:D67"/>
+    <mergeCell ref="A77:T77"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="S28:T35"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="P26:P27"/>
     <mergeCell ref="M42:M43"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="R42:R43"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="A20:A35"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="K3:R3"/>
-    <mergeCell ref="A4:A19"/>
-    <mergeCell ref="B4:B19"/>
-    <mergeCell ref="S4:T11"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="C44:C59"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="Q34:Q35"/>
+    <mergeCell ref="F1:O2"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="B20:B35"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="S36:T43"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="AG27:AG28"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AH27:AH28"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="J12:J27"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="G31:G33"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="E12:E14"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="M13:M14"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="D4:D11"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="AE27:AE28"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="S20:T27"/>
     <mergeCell ref="M37:M38"/>
     <mergeCell ref="L37:L38"/>
     <mergeCell ref="K37:K38"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="B68:D69"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="P61:P62"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="D20:D27"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="P66:P67"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="R61:R62"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="R42:R43"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="K3:R3"/>
+    <mergeCell ref="S4:T11"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="D4:D11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J12:J27"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="S20:T27"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="AE27:AE28"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="AF27:AF28"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="AD27:AD28"/>
-    <mergeCell ref="AC27:AC28"/>
-    <mergeCell ref="AB27:AB28"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="AG27:AG28"/>
-    <mergeCell ref="AH27:AH28"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="R55:R56"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="C28:C43"/>
-    <mergeCell ref="A36:A51"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N55:N56"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="Q66:Q67"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="P18:P19"/>
     <mergeCell ref="R23:R24"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="F1:O2"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="S36:T43"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="D12:D19"/>
-    <mergeCell ref="S12:T19"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="S28:T35"/>
-    <mergeCell ref="B20:B35"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="M55:M56"/>
-    <mergeCell ref="D60:D67"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="A77:T77"/>
-    <mergeCell ref="N55:N56"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="R63:R64"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="Q66:Q67"/>
-    <mergeCell ref="P66:P67"/>
-    <mergeCell ref="M66:M67"/>
-    <mergeCell ref="N66:N67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="M45:M46"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="O61:O62"/>
-    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="M63:M64"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="P63:P64"/>
     <mergeCell ref="M61:M62"/>
-    <mergeCell ref="O63:O64"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="A72:E76"/>
-    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="N63:N64"/>
+    <mergeCell ref="O66:O67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="D44:D51"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="R53:R54"/>
+    <mergeCell ref="C60:C67"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="I63:I65"/>
     <mergeCell ref="N61:N62"/>
-    <mergeCell ref="O66:O67"/>
-    <mergeCell ref="P61:P62"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="H60:H62"/>
     <mergeCell ref="H66:H67"/>
-    <mergeCell ref="R61:R62"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="T52:T59"/>
+    <mergeCell ref="D52:D59"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="Q63:Q64"/>
-    <mergeCell ref="P63:P64"/>
-    <mergeCell ref="M63:M64"/>
-    <mergeCell ref="N63:N64"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="S44:T51"/>
-    <mergeCell ref="C12:C27"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="D44:D51"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="O10:O11"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="J4:J11"/>
-    <mergeCell ref="D20:D27"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="H47:H49"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="C60:C67"/>
-    <mergeCell ref="B68:D69"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="T60:T67"/>
-    <mergeCell ref="L55:L56"/>
-    <mergeCell ref="R58:R59"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="I47:I49"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="J60:J67"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="K61:K62"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="K66:K67"/>
-    <mergeCell ref="R66:R67"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="J68:T76"/>
-    <mergeCell ref="F72:I76"/>
-    <mergeCell ref="E79:P80"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="R53:R54"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="Q53:Q54"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="I50:I51"/>
     <mergeCell ref="E52:E54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="Q45:Q46"/>
     <mergeCell ref="Q61:Q62"/>
     <mergeCell ref="F70:G70"/>
     <mergeCell ref="E69:F69"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="L50:L51"/>
-    <mergeCell ref="P50:P51"/>
-    <mergeCell ref="M50:M51"/>
-    <mergeCell ref="N50:N51"/>
-    <mergeCell ref="O50:O51"/>
-    <mergeCell ref="D52:D59"/>
-    <mergeCell ref="T52:T59"/>
-    <mergeCell ref="F71:G71"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="H70:I70"/>
     <mergeCell ref="E63:E65"/>
     <mergeCell ref="F60:F62"/>
+    <mergeCell ref="P50:P51"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="M50:M51"/>
+    <mergeCell ref="N50:N51"/>
+    <mergeCell ref="K53:K54"/>
     <mergeCell ref="G69:I69"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="O50:O51"/>
+    <mergeCell ref="Q53:Q54"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="O61:O62"/>
+    <mergeCell ref="C12:C27"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="L55:L56"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="F72:I76"/>
+    <mergeCell ref="E79:P80"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="J60:J67"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="R66:R67"/>
+    <mergeCell ref="N66:N67"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="P42:P43"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="J44:J59"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="AE21:AE22"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="R26:R27"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="B52:B67"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="A52:A67"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="D28:D35"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="O63:O64"/>
+    <mergeCell ref="M66:M67"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="S12:T19"/>
+    <mergeCell ref="D12:D19"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:E76"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="T60:T67"/>
+    <mergeCell ref="J68:T76"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="S44:T51"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="K61:K62"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="R63:R64"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="J4:J11"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="L63:L64"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="I47:I49"/>
+    <mergeCell ref="G68:I68"/>
     <mergeCell ref="H71:I71"/>
   </mergeCells>
   <pageMargins left="0.118055555555556" right="0.275694444444444" top="0.157638888888889" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6110,7 +6108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BA103"/>
+  <dimension ref="A1:BB103"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="0.56640625" style="102"/>
@@ -13195,31 +13193,30 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="AK17:AK18"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AK20:AK21"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="M17:M18"/>
-    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AK14:AK15"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="AK11:AK12"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="AK20:AK21"/>
+    <mergeCell ref="AK2:AK3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
@@ -13228,7 +13225,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W1253"/>
+  <dimension ref="A1:X1253"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="4.4179688" style="1"/>
@@ -23891,77 +23888,77 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="I10:I12"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="I4:I6"/>
     <mergeCell ref="J4:J6"/>
-    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="J22:J24"/>
     <mergeCell ref="F16:F18"/>
     <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="I16:I18"/>
     <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="D13:D15"/>
     <mergeCell ref="F19:F21"/>
     <mergeCell ref="J25:J27"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D7:D9"/>
     <mergeCell ref="D25:D27"/>
+    <mergeCell ref="I7:I9"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="B7:B9"/>
+    <mergeCell ref="F4:F6"/>
     <mergeCell ref="I13:I15"/>
     <mergeCell ref="J10:J12"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="E19:E21"/>
   </mergeCells>
   <pageMargins left="0.118055555555556" right="0.275694444444444" top="0.157638888888889" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9"/>
@@ -23970,7 +23967,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="2" max="2" customWidth="0" width="10.0" style="1"/>
@@ -24458,13 +24455,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" customWidth="1" width="9.136719" style="102"/>
@@ -24734,6 +24730,5 @@
     <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>